--- a/src/test/resources/manual_TestCases/RunnerTestCaseMasterSheet.xlsx
+++ b/src/test/resources/manual_TestCases/RunnerTestCaseMasterSheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91902\IdeaProjects\Selenium_E2E_Automation_framework\src\test\resources\manual_TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE00D6E7-4880-4B7D-9D64-C7B508B4EA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032FAD6B-D6F2-45E8-BB9A-4BE7D7856914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task TC" sheetId="1" r:id="rId1"/>
     <sheet name="Milestone TC" sheetId="2" r:id="rId2"/>
+    <sheet name="TaskField TC" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="83">
   <si>
     <t>TEST_CASE_ID</t>
   </si>
@@ -210,6 +211,104 @@
 new milestone.
 Show on milestone
 </t>
+  </si>
+  <si>
+    <t>TC_MILESTONE_03</t>
+  </si>
+  <si>
+    <t>Verify in milestone listing under Actions column name edit milestone feature with all field edited is working.</t>
+  </si>
+  <si>
+    <t>Milestone Updated successfully message should come with green highlighted.</t>
+  </si>
+  <si>
+    <t>Updated changes should match with data added.</t>
+  </si>
+  <si>
+    <t>3. Click on Milestone tab</t>
+  </si>
+  <si>
+    <t>Create new milestone button should be visible.</t>
+  </si>
+  <si>
+    <t>4. In milestone listing under Actions column click on edit icon</t>
+  </si>
+  <si>
+    <t>5. update all field in edit milestone with data and click on update.</t>
+  </si>
+  <si>
+    <t>6. Check  in listing that updated fields are changed.</t>
+  </si>
+  <si>
+    <t>Edit milestone should pop up with update button.</t>
+  </si>
+  <si>
+    <t>6. Click dissmiss button on green highlighted pop up</t>
+  </si>
+  <si>
+    <t>green highlighted popup should disappear.</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Test Cases</t>
+  </si>
+  <si>
+    <t>Pre-Condition</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Steps </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected </t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Booking Listing title should show</t>
+  </si>
+  <si>
+    <t>3. Default Task field is selected,
+click create new task button</t>
+  </si>
+  <si>
+    <t>Create new Task title 
+should come and Create button should be disabled.</t>
+  </si>
+  <si>
+    <t>4. Fill all fields with the data
+provided in excel.</t>
+  </si>
+  <si>
+    <t>Create Button should Enable</t>
+  </si>
+  <si>
+    <t>5. Details provided will be displayed
+in list table below create new task button.</t>
+  </si>
+  <si>
+    <t>Task name,Task Description, Task code,
+Workflow type should show in listing.</t>
+  </si>
+  <si>
+    <t>1,Verify Create new task feature 
+is creating new task with all fields
+details filled except Events details and should be always Active.</t>
+  </si>
+  <si>
+    <t>TAKE FROM DataCreation.xlsx
+"sheet 3"</t>
   </si>
 </sst>
 </file>
@@ -340,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -373,6 +472,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -391,6 +505,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -406,20 +523,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,13 +872,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -774,14 +897,14 @@
         <v>17</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
@@ -796,12 +919,12 @@
         <v>21</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="15"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
@@ -816,12 +939,12 @@
         <v>24</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="15"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
         <v>26</v>
@@ -836,12 +959,12 @@
         <v>28</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="15"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
@@ -854,7 +977,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="15"/>
+      <c r="J6" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -869,16 +992,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD0B06F-D086-4938-9AA0-C3AEEEA0202B}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.5703125" customWidth="1"/>
-    <col min="6" max="6" width="52.140625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="56.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
   </cols>
@@ -899,7 +1023,7 @@
       <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="13" t="s">
@@ -915,230 +1039,369 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:10" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="26" t="s">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="28" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="17"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="28" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="17"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="25" t="s">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="17"/>
-    </row>
-    <row r="6" spans="1:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="26" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="17"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="28" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-    </row>
-    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="26" t="s">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="28" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="26"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="28" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="26"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="25" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" ht="195" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="26" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="28" t="s">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="B14:B21"/>
     <mergeCell ref="J2:J6"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="B2:B7"/>
@@ -1149,4 +1412,148 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB0E45C-7795-45DB-91BC-39286BE77C7F}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>